--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft12474759-my.sharepoint.com/personal/etienne_desrochers_xnnov_com/Documents/Documents/GitHub/Nouveau dossier (2)/QuantumB/order_file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{71E589D0-2AD9-4317-8FC6-2B242785F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACD826D-CF2B-4264-B2C4-31AAD95A06D1}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{71E589D0-2AD9-4317-8FC6-2B242785F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9964D9A-AB72-4ACB-9C74-634F534C4030}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
   <si>
     <t>Cool_En</t>
   </si>
@@ -364,13 +364,37 @@
   </si>
   <si>
     <t>EEV-VI_En3</t>
+  </si>
+  <si>
+    <t>RESERVED1</t>
+  </si>
+  <si>
+    <t>RESERVED2</t>
+  </si>
+  <si>
+    <t>RESERVED3</t>
+  </si>
+  <si>
+    <t>RESERVED4</t>
+  </si>
+  <si>
+    <t>RESERVED5</t>
+  </si>
+  <si>
+    <t>RESERVED6</t>
+  </si>
+  <si>
+    <t>RESERVED7</t>
+  </si>
+  <si>
+    <t>RESERVED8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +416,12 @@
     <font>
       <sz val="18"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -864,7 +894,9 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="C9" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1070,9 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="3"/>
+      <c r="B25" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="C25">
         <v>1</v>
       </c>
@@ -1212,7 +1246,9 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="3"/>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="C41">
         <v>2</v>
       </c>
@@ -1386,7 +1422,9 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="3"/>
+      <c r="B57" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="C57">
         <v>3</v>
       </c>
@@ -1395,7 +1433,9 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="3"/>
+      <c r="B58" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="C58" t="s">
         <v>55</v>
       </c>
@@ -1404,7 +1444,9 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="3"/>
+      <c r="B59" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="C59" t="s">
         <v>55</v>
       </c>
@@ -1413,7 +1455,9 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="3"/>
+      <c r="B60" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="C60" t="s">
         <v>55</v>
       </c>
@@ -1422,7 +1466,9 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="3"/>
+      <c r="B61" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="C61" t="s">
         <v>55</v>
       </c>
@@ -1869,6 +1915,7 @@
       <c r="B208" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft12474759-my.sharepoint.com/personal/etienne_desrochers_xnnov_com/Documents/Documents/GitHub/Nouveau dossier (2)/QuantumB/order_file/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thomas Goulet\Documents\GitHub\QuantumB\order_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{71E589D0-2AD9-4317-8FC6-2B242785F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9964D9A-AB72-4ACB-9C74-634F534C4030}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05D33D0-F363-482E-814F-6A1F9D38F8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
     <sheet name="Output" sheetId="2" r:id="rId2"/>
+    <sheet name="Output (2)" sheetId="4" r:id="rId3"/>
+    <sheet name="Input (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="139">
   <si>
     <t>Cool_En</t>
   </si>
@@ -388,13 +390,82 @@
   </si>
   <si>
     <t>RESERVED8</t>
+  </si>
+  <si>
+    <t>HW_FSw</t>
+  </si>
+  <si>
+    <t>CW_FSw</t>
+  </si>
+  <si>
+    <t>HRW_SV_Fdk</t>
+  </si>
+  <si>
+    <t>HRW_XV_Fdk</t>
+  </si>
+  <si>
+    <t>CW_STemp</t>
+  </si>
+  <si>
+    <t>CW_XTemp</t>
+  </si>
+  <si>
+    <t>HW_STemp</t>
+  </si>
+  <si>
+    <t>HW_XTemp</t>
+  </si>
+  <si>
+    <t>CW_SV_Fdk</t>
+  </si>
+  <si>
+    <t>CW_XV_Fdk</t>
+  </si>
+  <si>
+    <t>HW_SV_Fdk</t>
+  </si>
+  <si>
+    <t>HW_XV_Fdk</t>
+  </si>
+  <si>
+    <t>CW_SVlv</t>
+  </si>
+  <si>
+    <t>CW_XVlv</t>
+  </si>
+  <si>
+    <t>HW_SVlv</t>
+  </si>
+  <si>
+    <t>HW_XVlv</t>
+  </si>
+  <si>
+    <t>HRW_SVlv</t>
+  </si>
+  <si>
+    <t>HRW_XVlv</t>
+  </si>
+  <si>
+    <t>reserved1</t>
+  </si>
+  <si>
+    <t>reserved2</t>
+  </si>
+  <si>
+    <t>reserved3</t>
+  </si>
+  <si>
+    <t>reserved4</t>
+  </si>
+  <si>
+    <t>reserved5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,8 +497,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,8 +523,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -449,11 +544,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -461,6 +578,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,7 +607,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -796,7 +924,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6AF293-B920-4C3D-B4F7-D48127D2B848}">
   <dimension ref="A1:C208"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -817,7 +945,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
@@ -828,7 +956,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -839,7 +967,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
@@ -850,7 +978,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
@@ -861,7 +989,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
@@ -872,7 +1000,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
@@ -883,8 +1011,8 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
+      <c r="B8" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
@@ -894,8 +1022,8 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>108</v>
+      <c r="B9" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
@@ -905,7 +1033,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C10">
@@ -916,7 +1044,7 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C11">
@@ -927,7 +1055,7 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C12">
@@ -938,7 +1066,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C13">
@@ -949,7 +1077,7 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C14">
@@ -960,7 +1088,7 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C15">
@@ -971,7 +1099,7 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C16">
@@ -982,7 +1110,7 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C17">
@@ -993,7 +1121,7 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C18">
@@ -1004,7 +1132,7 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C19">
@@ -1015,7 +1143,7 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C20">
@@ -1026,7 +1154,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C21">
@@ -1037,7 +1165,7 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C22">
@@ -1048,7 +1176,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C23">
@@ -1059,7 +1187,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C24">
@@ -1070,18 +1198,18 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
+      <c r="B25" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C26">
@@ -1092,7 +1220,7 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="12" t="s">
         <v>23</v>
       </c>
       <c r="C27">
@@ -1103,7 +1231,7 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C28">
@@ -1114,7 +1242,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C29">
@@ -1125,7 +1253,7 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C30">
@@ -1136,7 +1264,7 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C31">
@@ -1147,7 +1275,7 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C32">
@@ -1158,7 +1286,7 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C33">
@@ -1169,7 +1297,7 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C34">
@@ -1180,7 +1308,7 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C35">
@@ -1191,7 +1319,7 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C36">
@@ -1202,7 +1330,7 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C37">
@@ -1213,7 +1341,7 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C38">
@@ -1224,7 +1352,7 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C39">
@@ -1235,7 +1363,7 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C40">
@@ -1246,232 +1374,136 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C41">
-        <v>2</v>
+      <c r="B41" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42">
-        <v>3</v>
+      <c r="B42" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43">
-        <v>3</v>
+      <c r="B43" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44">
-        <v>3</v>
+      <c r="B44" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45">
-        <v>3</v>
+      <c r="B45" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46">
-        <v>3</v>
+      <c r="B46" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47">
-        <v>3</v>
+      <c r="B47" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48">
-        <v>3</v>
+      <c r="B48" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49">
-        <v>3</v>
+      <c r="B49" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
+      <c r="B50" s="3"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51">
-        <v>3</v>
-      </c>
+      <c r="B51" s="3"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
+      <c r="B52" s="3"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53">
-        <v>3</v>
-      </c>
+      <c r="B53" s="3"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54">
-        <v>3</v>
-      </c>
+      <c r="B54" s="3"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
+      <c r="B55" s="3"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C56">
-        <v>3</v>
-      </c>
+      <c r="B56" s="4"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
+      <c r="B57" s="4"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C58" t="s">
-        <v>55</v>
-      </c>
+      <c r="B58" s="4"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C59" t="s">
-        <v>55</v>
-      </c>
+      <c r="B59" s="4"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C60" t="s">
-        <v>55</v>
-      </c>
+      <c r="B60" s="4"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" t="s">
-        <v>55</v>
-      </c>
+      <c r="B61" s="4"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
@@ -1922,8 +1954,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6301306-2788-4A1B-8F97-09FC2002C8B2}">
-  <dimension ref="A1:C58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1946,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1957,7 +1989,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1968,10 +2000,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1979,10 +2011,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1990,10 +2022,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2001,10 +2033,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2023,7 +2055,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2034,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2045,7 +2077,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2056,7 +2088,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2100,7 +2132,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2111,7 +2143,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2122,7 +2154,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2133,7 +2165,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2144,7 +2176,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2155,7 +2187,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2166,7 +2198,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2176,6 +2208,9 @@
       <c r="A23">
         <v>22</v>
       </c>
+      <c r="B23" t="s">
+        <v>134</v>
+      </c>
       <c r="C23">
         <v>1</v>
       </c>
@@ -2184,6 +2219,9 @@
       <c r="A24">
         <v>23</v>
       </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
       <c r="C24">
         <v>1</v>
       </c>
@@ -2215,7 +2253,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2226,7 +2264,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -2237,7 +2275,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -2248,7 +2286,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -2292,7 +2330,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -2303,7 +2341,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -2314,7 +2352,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -2325,7 +2363,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -2336,7 +2374,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2347,7 +2385,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -2358,7 +2396,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -2368,6 +2406,9 @@
       <c r="A41">
         <v>40</v>
       </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
       <c r="C41">
         <v>2</v>
       </c>
@@ -2376,6 +2417,9 @@
       <c r="A42">
         <v>41</v>
       </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
       <c r="C42">
         <v>2</v>
       </c>
@@ -2384,6 +2428,483 @@
       <c r="A43">
         <v>42</v>
       </c>
+      <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA1C704-F4A3-4AD1-BE4D-6C38CFBFD783}">
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="24" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
       <c r="C43">
         <v>2</v>
       </c>
@@ -2552,6 +3073,1132 @@
       <c r="C58">
         <v>3</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4D250D-3971-4094-BD24-089E8C81E49E}">
+  <dimension ref="A1:C208"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="24" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="3"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="3"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="3"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="3"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="3"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="3"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="3"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="3"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="3"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="3"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="3"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" s="3"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="3"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B177" s="3"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="3"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="3"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" s="3"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="3"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" s="3"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" s="3"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="3"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="3"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="3"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="3"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="3"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="3"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="3"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="3"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="3"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="3"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="3"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="3"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="3"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="3"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="3"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="3"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="3"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="3"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B208" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thomas Goulet\Documents\GitHub\QuantumB\order_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05D33D0-F363-482E-814F-6A1F9D38F8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="140">
   <si>
     <t>Cool_En</t>
   </si>
@@ -459,6 +459,9 @@
   </si>
   <si>
     <t>reserved5</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
@@ -1980,8 +1983,8 @@
       <c r="B2" t="s">
         <v>128</v>
       </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="C2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1991,8 +1994,8 @@
       <c r="B3" t="s">
         <v>129</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="C3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2002,8 +2005,8 @@
       <c r="B4" t="s">
         <v>130</v>
       </c>
-      <c r="C4">
-        <v>1</v>
+      <c r="C4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2013,8 +2016,8 @@
       <c r="B5" t="s">
         <v>131</v>
       </c>
-      <c r="C5">
-        <v>1</v>
+      <c r="C5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2024,8 +2027,8 @@
       <c r="B6" t="s">
         <v>132</v>
       </c>
-      <c r="C6">
-        <v>1</v>
+      <c r="C6" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2035,8 +2038,8 @@
       <c r="B7" t="s">
         <v>133</v>
       </c>
-      <c r="C7">
-        <v>1</v>
+      <c r="C7" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thomas Goulet\Documents\GitHub\QuantumB\order_file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft12474759-my.sharepoint.com/personal/etienne_desrochers_xnnov_com/Documents/Documents/GitHub/Nouveau dossier (2)/QuantumB/order_file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C01EBE-A2E8-4591-947F-6D0B59B75C66}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="141">
   <si>
     <t>Cool_En</t>
   </si>
@@ -461,7 +461,10 @@
     <t>reserved5</t>
   </si>
   <si>
-    <t>n</t>
+    <t xml:space="preserve">IOTYPE </t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -610,7 +613,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -926,14 +929,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6AF293-B920-4C3D-B4F7-D48127D2B848}">
-  <dimension ref="A1:C208"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D208"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -943,8 +946,11 @@
       <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -954,8 +960,11 @@
       <c r="C2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -965,8 +974,11 @@
       <c r="C3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -976,8 +988,11 @@
       <c r="C4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -987,8 +1002,11 @@
       <c r="C5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -998,8 +1016,11 @@
       <c r="C6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1009,8 +1030,11 @@
       <c r="C7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1020,8 +1044,11 @@
       <c r="C8" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1031,8 +1058,11 @@
       <c r="C9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1043,7 +1073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1054,7 +1084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1065,7 +1095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1076,7 +1106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1087,7 +1117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1098,7 +1128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1109,7 +1139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1120,7 +1150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1131,7 +1161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1142,7 +1172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1153,7 +1183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1164,7 +1194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1175,7 +1205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1186,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1197,7 +1227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1207,8 +1237,11 @@
       <c r="C25" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1219,7 +1252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1230,7 +1263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1241,7 +1274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1252,7 +1285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1263,7 +1296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1274,7 +1307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1285,7 +1318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1296,7 +1329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1307,7 +1340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1318,7 +1351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1329,7 +1362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1340,7 +1373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1351,7 +1384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1362,7 +1395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1373,7 +1406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1383,8 +1416,11 @@
       <c r="C41" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1394,8 +1430,11 @@
       <c r="C42" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1405,8 +1444,11 @@
       <c r="C43" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1416,8 +1458,11 @@
       <c r="C44" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1427,8 +1472,11 @@
       <c r="C45" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1438,8 +1486,11 @@
       <c r="C46" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1449,8 +1500,11 @@
       <c r="C47" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1460,8 +1514,11 @@
       <c r="C48" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1471,50 +1528,53 @@
       <c r="C49" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B50" s="3"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B51" s="3"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B52" s="3"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B56" s="4"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B57" s="4"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59" s="4"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="4"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="4"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B64" s="3"/>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
@@ -1957,8 +2017,521 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6301306-2788-4A1B-8F97-09FC2002C8B2}">
-  <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA1C704-F4A3-4AD1-BE4D-6C38CFBFD783}">
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1981,495 +2554,6 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>137</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>138</v>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA1C704-F4A3-4AD1-BE4D-6C38CFBFD783}">
-  <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="24" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
         <v>56</v>
       </c>
       <c r="C2">
@@ -3085,7 +3169,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4D250D-3971-4094-BD24-089E8C81E49E}">
   <dimension ref="A1:C208"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C01EBE-A2E8-4591-947F-6D0B59B75C66}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
+    <workbookView xWindow="-14670" yWindow="21900" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft12474759-my.sharepoint.com/personal/etienne_desrochers_xnnov_com/Documents/Documents/GitHub/Nouveau dossier (2)/QuantumB/order_file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C01EBE-A2E8-4591-947F-6D0B59B75C66}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{761D9B5C-7F7C-4F5B-B231-8F6858C03C62}"/>
   <bookViews>
-    <workbookView xWindow="-14670" yWindow="21900" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="142">
   <si>
     <t>Cool_En</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>non connecterO</t>
   </si>
 </sst>
 </file>
@@ -2050,7 +2053,7 @@
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2064,7 +2067,7 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2078,7 +2081,7 @@
         <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2092,7 +2095,7 @@
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2106,7 +2109,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2120,7 +2123,7 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2321,7 +2324,7 @@
         <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft12474759-my.sharepoint.com/personal/etienne_desrochers_xnnov_com/Documents/Documents/GitHub/Nouveau dossier (2)/QuantumB/order_file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{761D9B5C-7F7C-4F5B-B231-8F6858C03C62}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{350BB699-73BC-4514-8150-C53C08D512C4}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
@@ -2026,6 +2026,7 @@
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft12474759-my.sharepoint.com/personal/etienne_desrochers_xnnov_com/Documents/Documents/GitHub/Nouveau dossier (2)/QuantumB/order_file/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Etienne Desrochers\Documents\QuantumB\order_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{FC32E15D-D226-49D6-8939-7DC56521B1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{350BB699-73BC-4514-8150-C53C08D512C4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EEC90F-BE34-4302-ADF9-DDB5D2A0B93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
+    <workbookView xWindow="-38520" yWindow="300" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="167">
   <si>
     <t>Cool_En</t>
   </si>
@@ -392,82 +392,157 @@
     <t>RESERVED8</t>
   </si>
   <si>
-    <t>HW_FSw</t>
-  </si>
-  <si>
-    <t>CW_FSw</t>
-  </si>
-  <si>
-    <t>HRW_SV_Fdk</t>
-  </si>
-  <si>
-    <t>HRW_XV_Fdk</t>
-  </si>
-  <si>
-    <t>CW_STemp</t>
-  </si>
-  <si>
-    <t>CW_XTemp</t>
-  </si>
-  <si>
-    <t>HW_STemp</t>
-  </si>
-  <si>
-    <t>HW_XTemp</t>
-  </si>
-  <si>
-    <t>CW_SV_Fdk</t>
-  </si>
-  <si>
-    <t>CW_XV_Fdk</t>
-  </si>
-  <si>
-    <t>HW_SV_Fdk</t>
-  </si>
-  <si>
-    <t>HW_XV_Fdk</t>
-  </si>
-  <si>
-    <t>CW_SVlv</t>
-  </si>
-  <si>
-    <t>CW_XVlv</t>
-  </si>
-  <si>
-    <t>HW_SVlv</t>
-  </si>
-  <si>
-    <t>HW_XVlv</t>
-  </si>
-  <si>
-    <t>HRW_SVlv</t>
-  </si>
-  <si>
-    <t>HRW_XVlv</t>
-  </si>
-  <si>
-    <t>reserved1</t>
-  </si>
-  <si>
-    <t>reserved2</t>
-  </si>
-  <si>
-    <t>reserved3</t>
-  </si>
-  <si>
-    <t>reserved4</t>
-  </si>
-  <si>
-    <t>reserved5</t>
-  </si>
-  <si>
     <t xml:space="preserve">IOTYPE </t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>non connecterO</t>
+    <t>FIRE_ALM</t>
+  </si>
+  <si>
+    <t>MAU_EN</t>
+  </si>
+  <si>
+    <t>SA_SP</t>
+  </si>
+  <si>
+    <t>RH_SP</t>
+  </si>
+  <si>
+    <t>ResetB</t>
+  </si>
+  <si>
+    <t>DXLT</t>
+  </si>
+  <si>
+    <t>OAH</t>
+  </si>
+  <si>
+    <t>SAT</t>
+  </si>
+  <si>
+    <t>SAH</t>
+  </si>
+  <si>
+    <t>RAT</t>
+  </si>
+  <si>
+    <t>RAH</t>
+  </si>
+  <si>
+    <t>EAT</t>
+  </si>
+  <si>
+    <t>EAH</t>
+  </si>
+  <si>
+    <t>SAP</t>
+  </si>
+  <si>
+    <t>RAP</t>
+  </si>
+  <si>
+    <t>SF_STS1</t>
+  </si>
+  <si>
+    <t>SF_STS2</t>
+  </si>
+  <si>
+    <t>SF_STS3</t>
+  </si>
+  <si>
+    <t>SF_STS4</t>
+  </si>
+  <si>
+    <t>SF_STS5</t>
+  </si>
+  <si>
+    <t>SF_STS6</t>
+  </si>
+  <si>
+    <t>RF-STS1</t>
+  </si>
+  <si>
+    <t>RF-STS2</t>
+  </si>
+  <si>
+    <t>RF-STS3</t>
+  </si>
+  <si>
+    <t>RF-STS4</t>
+  </si>
+  <si>
+    <t>RF-STS5</t>
+  </si>
+  <si>
+    <t>RF-STS6</t>
+  </si>
+  <si>
+    <t>OADAMPER_STS1</t>
+  </si>
+  <si>
+    <t>OADAMPER_STS2</t>
+  </si>
+  <si>
+    <t>EADAMPER_STS1</t>
+  </si>
+  <si>
+    <t>EADAMPER_STS2</t>
+  </si>
+  <si>
+    <t>PRE_FILTER_P</t>
+  </si>
+  <si>
+    <t>FINAL_FILTER_P</t>
+  </si>
+  <si>
+    <t>Reserve1</t>
+  </si>
+  <si>
+    <t>Reserve2</t>
+  </si>
+  <si>
+    <t>Status Box</t>
+  </si>
+  <si>
+    <t>18v</t>
+  </si>
+  <si>
+    <t>SUPP-F_EN</t>
+  </si>
+  <si>
+    <t>SUPP-F_MOD</t>
+  </si>
+  <si>
+    <t>RTRN-F_EN</t>
+  </si>
+  <si>
+    <t>RTRN-F_MOD</t>
+  </si>
+  <si>
+    <t>OADAMPER_MOD</t>
+  </si>
+  <si>
+    <t>EADAMPER_MOD</t>
+  </si>
+  <si>
+    <t>ENT_WH_EN</t>
+  </si>
+  <si>
+    <t>ENT_WH_MOD</t>
+  </si>
+  <si>
+    <t>GAS_HEAT_EN</t>
+  </si>
+  <si>
+    <t>GAS_HEAT_MOD</t>
+  </si>
+  <si>
+    <t>Modulation</t>
+  </si>
+  <si>
+    <t>Enable</t>
   </si>
 </sst>
 </file>
@@ -579,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -587,14 +662,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -936,7 +1006,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
@@ -950,119 +1020,119 @@
         <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>0</v>
+      <c r="B2" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>1</v>
+      <c r="B3" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="C3" t="s">
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>2</v>
+      <c r="B4" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="C4" t="s">
         <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>3</v>
+      <c r="B5" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>4</v>
+      <c r="B6" s="7" t="s">
+        <v>151</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>5</v>
+      <c r="B7" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>116</v>
+      <c r="B8" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
         <v>117</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1070,21 +1140,27 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
+      <c r="B11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1092,21 +1168,27 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
+        <v>125</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
+      <c r="B13" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1114,21 +1196,27 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
+      <c r="B15" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1136,87 +1224,111 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
+      <c r="B17" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
+      <c r="B18" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
+      <c r="B19" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
+      <c r="B20" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
+      <c r="B21" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
+      <c r="B22" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
+      <c r="B23" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1224,360 +1336,276 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>118</v>
+      <c r="B25" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="C25" t="s">
         <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
+      <c r="B26" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
+      <c r="B27" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
+      <c r="B28" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
+      <c r="B29" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
+      <c r="B30" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
+      <c r="B31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
+      <c r="B32" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
+      <c r="B33" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
+      <c r="B34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35">
-        <v>2</v>
+      <c r="B35" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
+      <c r="B36" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
+      <c r="B37" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
+      <c r="B38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
+      <c r="B39" s="9"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
+      <c r="B40" s="5"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" t="s">
-        <v>140</v>
-      </c>
+      <c r="B41" s="6"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" t="s">
-        <v>140</v>
-      </c>
+      <c r="B42" s="10"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" t="s">
-        <v>140</v>
-      </c>
+      <c r="B43" s="6"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" t="s">
-        <v>140</v>
-      </c>
+      <c r="B44" s="10"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C45" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" t="s">
-        <v>140</v>
-      </c>
+      <c r="B45" s="6"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" t="s">
-        <v>140</v>
-      </c>
+      <c r="B46" s="10"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" t="s">
-        <v>140</v>
-      </c>
+      <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="10"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="6"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="3"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="3"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="4"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="4"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="4"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="4"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B64" s="3"/>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
@@ -2020,11 +2048,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6301306-2788-4A1B-8F97-09FC2002C8B2}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
   </cols>
@@ -2040,490 +2068,147 @@
         <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>128</v>
+      <c r="B2" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>129</v>
+      <c r="B3" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="C3" t="s">
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>130</v>
+      <c r="B4" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="C4" t="s">
         <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>131</v>
+      <c r="B5" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>132</v>
+      <c r="B6" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>133</v>
+      <c r="B7" s="9" t="s">
+        <v>160</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
+      <c r="B8" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
+      <c r="B9" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
+      <c r="B10" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>137</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>138</v>
-      </c>
-      <c r="C43">
-        <v>2</v>
+      <c r="B11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/order_file/Order_IO.xlsx
+++ b/order_file/Order_IO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Etienne Desrochers\Documents\QuantumB\order_file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft12474759-my.sharepoint.com/personal/etienne_desrochers_xnnov_com/Documents/Documents/GitHub/Nouveau dossier (2)/QuantumB/order_file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EEC90F-BE34-4302-ADF9-DDB5D2A0B93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{91EEC90F-BE34-4302-ADF9-DDB5D2A0B93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B00BDCF-F747-43B4-B594-DC990F1C7C7E}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="300" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C2DDF0E3-580A-4B29-B2E2-7B10314745D6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="138">
   <si>
     <t>Cool_En</t>
   </si>
@@ -395,154 +395,67 @@
     <t xml:space="preserve">IOTYPE </t>
   </si>
   <si>
+    <t>LOL1</t>
+  </si>
+  <si>
+    <t>Cd_Sts2-C</t>
+  </si>
+  <si>
+    <t>LOL2</t>
+  </si>
+  <si>
+    <t>Cd_Sts3-C</t>
+  </si>
+  <si>
+    <t>LOL3</t>
+  </si>
+  <si>
+    <t>Reserved1</t>
+  </si>
+  <si>
+    <t>Reserved2</t>
+  </si>
+  <si>
+    <t>Reserved3</t>
+  </si>
+  <si>
+    <t>HT_En1</t>
+  </si>
+  <si>
+    <t>HT_En2</t>
+  </si>
+  <si>
+    <t>HT_En3</t>
+  </si>
+  <si>
+    <t>ReservedO1</t>
+  </si>
+  <si>
+    <t>ReservedO2</t>
+  </si>
+  <si>
+    <t>ReservedO3</t>
+  </si>
+  <si>
+    <t>ReservedO4</t>
+  </si>
+  <si>
+    <t>ReservedO5</t>
+  </si>
+  <si>
+    <t>ReservedO6</t>
+  </si>
+  <si>
+    <t>non connecter</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>FIRE_ALM</t>
-  </si>
-  <si>
-    <t>MAU_EN</t>
-  </si>
-  <si>
-    <t>SA_SP</t>
-  </si>
-  <si>
-    <t>RH_SP</t>
-  </si>
-  <si>
-    <t>ResetB</t>
-  </si>
-  <si>
-    <t>DXLT</t>
-  </si>
-  <si>
-    <t>OAH</t>
-  </si>
-  <si>
-    <t>SAT</t>
-  </si>
-  <si>
-    <t>SAH</t>
-  </si>
-  <si>
-    <t>RAT</t>
-  </si>
-  <si>
-    <t>RAH</t>
-  </si>
-  <si>
-    <t>EAT</t>
-  </si>
-  <si>
-    <t>EAH</t>
-  </si>
-  <si>
-    <t>SAP</t>
-  </si>
-  <si>
-    <t>RAP</t>
-  </si>
-  <si>
-    <t>SF_STS1</t>
-  </si>
-  <si>
-    <t>SF_STS2</t>
-  </si>
-  <si>
-    <t>SF_STS3</t>
-  </si>
-  <si>
-    <t>SF_STS4</t>
-  </si>
-  <si>
-    <t>SF_STS5</t>
-  </si>
-  <si>
-    <t>SF_STS6</t>
-  </si>
-  <si>
-    <t>RF-STS1</t>
-  </si>
-  <si>
-    <t>RF-STS2</t>
-  </si>
-  <si>
-    <t>RF-STS3</t>
-  </si>
-  <si>
-    <t>RF-STS4</t>
-  </si>
-  <si>
-    <t>RF-STS5</t>
-  </si>
-  <si>
-    <t>RF-STS6</t>
-  </si>
-  <si>
-    <t>OADAMPER_STS1</t>
-  </si>
-  <si>
-    <t>OADAMPER_STS2</t>
-  </si>
-  <si>
-    <t>EADAMPER_STS1</t>
-  </si>
-  <si>
-    <t>EADAMPER_STS2</t>
-  </si>
-  <si>
-    <t>PRE_FILTER_P</t>
-  </si>
-  <si>
-    <t>FINAL_FILTER_P</t>
-  </si>
-  <si>
-    <t>Reserve1</t>
-  </si>
-  <si>
-    <t>Reserve2</t>
-  </si>
-  <si>
-    <t>Status Box</t>
-  </si>
-  <si>
-    <t>18v</t>
-  </si>
-  <si>
-    <t>SUPP-F_EN</t>
-  </si>
-  <si>
-    <t>SUPP-F_MOD</t>
-  </si>
-  <si>
-    <t>RTRN-F_EN</t>
-  </si>
-  <si>
-    <t>RTRN-F_MOD</t>
-  </si>
-  <si>
-    <t>OADAMPER_MOD</t>
-  </si>
-  <si>
-    <t>EADAMPER_MOD</t>
-  </si>
-  <si>
-    <t>ENT_WH_EN</t>
-  </si>
-  <si>
-    <t>ENT_WH_MOD</t>
-  </si>
-  <si>
-    <t>GAS_HEAT_EN</t>
-  </si>
-  <si>
-    <t>GAS_HEAT_MOD</t>
-  </si>
-  <si>
-    <t>Modulation</t>
-  </si>
-  <si>
-    <t>Enable</t>
+    <t>Pressure</t>
+  </si>
+  <si>
+    <t>non connecterO</t>
   </si>
 </sst>
 </file>
@@ -594,7 +507,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -609,18 +522,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -650,6 +557,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -662,12 +580,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1007,6 +925,7 @@
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
@@ -1027,14 +946,14 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1042,27 +961,27 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1070,55 +989,55 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" t="s">
-        <v>55</v>
+      <c r="B7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
+      <c r="B8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1126,27 +1045,27 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
+      <c r="B10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1154,27 +1073,27 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
+      <c r="B12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1182,27 +1101,27 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
+      <c r="B14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1210,55 +1129,55 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
+      <c r="B16" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
+      <c r="B17" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
+      <c r="B18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1266,27 +1185,27 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
+      <c r="B20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1294,27 +1213,27 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
         <v>135</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1322,27 +1241,27 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
+        <v>118</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" t="s">
-        <v>55</v>
+      <c r="B24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1350,27 +1269,27 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
+        <v>29</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" t="s">
-        <v>55</v>
+      <c r="B26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1378,27 +1297,27 @@
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" t="s">
-        <v>55</v>
+      <c r="B28" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1406,27 +1325,27 @@
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C29" t="s">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" t="s">
-        <v>55</v>
+      <c r="B30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,55 +1353,55 @@
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" t="s">
-        <v>55</v>
+        <v>35</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C32" t="s">
-        <v>55</v>
+      <c r="B32" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" t="s">
-        <v>55</v>
+      <c r="B33" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" t="s">
-        <v>55</v>
+      <c r="B34" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1490,27 +1409,27 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" t="s">
-        <v>55</v>
+        <v>38</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C36" t="s">
-        <v>55</v>
+      <c r="B36" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,94 +1437,226 @@
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C37" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="9"/>
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="5"/>
+      <c r="A40">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="6"/>
+      <c r="A41">
+        <v>36</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="10"/>
+      <c r="A42">
+        <v>36</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="6"/>
+      <c r="A43">
+        <v>36</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="10"/>
+      <c r="A44">
+        <v>36</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="6"/>
+      <c r="A45">
+        <v>36</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="10"/>
+      <c r="A46">
+        <v>36</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="6"/>
+      <c r="A47">
+        <v>36</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="10"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="6"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>36</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>36</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B50" s="3"/>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B51" s="3"/>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B52" s="3"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B56" s="4"/>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B57" s="4"/>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59" s="4"/>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="4"/>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="4"/>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B64" s="3"/>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
@@ -2048,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6301306-2788-4A1B-8F97-09FC2002C8B2}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -2075,140 +2126,756 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
+      <c r="B2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
+      <c r="B3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
+      <c r="B4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
+      <c r="B5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
+      <c r="B6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" t="s">
-        <v>55</v>
+      <c r="B7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
+      <c r="B8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
+      <c r="B9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
+      <c r="B10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
+      <c r="B11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
